--- a/Server/Common/GameDatasheet/Original_Warrior_Level_Data.xlsx
+++ b/Server/Common/GameDatasheet/Original_Warrior_Level_Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zmwps\Desktop\Project_MMORPG\Server\Common\GameDatasheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D0744EC-8D08-4019-AEA3-5F8CE3D620E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A04FBD9F-480C-4F8C-8C6A-8DCE2E80EA35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{FDA0E9BE-2965-48E7-917D-7535984AEDF4}"/>
   </bookViews>
@@ -39,19 +39,19 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>base_attack</t>
+    <t>SERVER</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>base_magic</t>
+    <t>physical_attack</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>max_exp</t>
+    <t>magical_attack</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>SERVER</t>
+    <t>exp_requirement</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -438,33 +438,33 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="D2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="F2" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.4">
@@ -481,7 +481,7 @@
         <v>10</v>
       </c>
       <c r="E3">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F3">
         <v>50</v>
@@ -501,7 +501,7 @@
         <v>20</v>
       </c>
       <c r="E4">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F4">
         <v>80</v>
@@ -521,7 +521,7 @@
         <v>30</v>
       </c>
       <c r="E5">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F5">
         <v>110</v>
@@ -541,7 +541,7 @@
         <v>40</v>
       </c>
       <c r="E6">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F6">
         <v>140</v>
@@ -561,7 +561,7 @@
         <v>50</v>
       </c>
       <c r="E7">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F7">
         <v>170</v>
@@ -581,7 +581,7 @@
         <v>60</v>
       </c>
       <c r="E8">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="F8">
         <v>200</v>
@@ -601,7 +601,7 @@
         <v>70</v>
       </c>
       <c r="E9">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="F9">
         <v>230</v>
@@ -621,7 +621,7 @@
         <v>80</v>
       </c>
       <c r="E10">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="F10">
         <v>260</v>
@@ -641,7 +641,7 @@
         <v>90</v>
       </c>
       <c r="E11">
-        <v>45</v>
+        <v>18</v>
       </c>
       <c r="F11">
         <v>290</v>
@@ -661,7 +661,7 @@
         <v>100</v>
       </c>
       <c r="E12">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="F12">
         <v>320</v>
@@ -681,7 +681,7 @@
         <v>110</v>
       </c>
       <c r="E13">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="F13">
         <v>350</v>
@@ -701,7 +701,7 @@
         <v>120</v>
       </c>
       <c r="E14">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="F14">
         <v>380</v>
@@ -721,7 +721,7 @@
         <v>130</v>
       </c>
       <c r="E15">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="F15">
         <v>410</v>
@@ -741,7 +741,7 @@
         <v>140</v>
       </c>
       <c r="E16">
-        <v>70</v>
+        <v>28</v>
       </c>
       <c r="F16">
         <v>440</v>
@@ -761,7 +761,7 @@
         <v>150</v>
       </c>
       <c r="E17">
-        <v>75</v>
+        <v>30</v>
       </c>
       <c r="F17">
         <v>470</v>
@@ -781,7 +781,7 @@
         <v>160</v>
       </c>
       <c r="E18">
-        <v>80</v>
+        <v>32</v>
       </c>
       <c r="F18">
         <v>500</v>
@@ -801,7 +801,7 @@
         <v>170</v>
       </c>
       <c r="E19">
-        <v>85</v>
+        <v>34</v>
       </c>
       <c r="F19">
         <v>530</v>
@@ -821,7 +821,7 @@
         <v>180</v>
       </c>
       <c r="E20">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="F20">
         <v>560</v>
@@ -841,7 +841,7 @@
         <v>190</v>
       </c>
       <c r="E21">
-        <v>95</v>
+        <v>38</v>
       </c>
       <c r="F21">
         <v>590</v>
@@ -861,7 +861,7 @@
         <v>200</v>
       </c>
       <c r="E22">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="F22">
         <v>620</v>
@@ -881,7 +881,7 @@
         <v>210</v>
       </c>
       <c r="E23">
-        <v>105</v>
+        <v>42</v>
       </c>
       <c r="F23">
         <v>650</v>
@@ -901,7 +901,7 @@
         <v>220</v>
       </c>
       <c r="E24">
-        <v>110</v>
+        <v>44</v>
       </c>
       <c r="F24">
         <v>680</v>
@@ -921,7 +921,7 @@
         <v>230</v>
       </c>
       <c r="E25">
-        <v>115</v>
+        <v>46</v>
       </c>
       <c r="F25">
         <v>710</v>
@@ -941,7 +941,7 @@
         <v>240</v>
       </c>
       <c r="E26">
-        <v>120</v>
+        <v>48</v>
       </c>
       <c r="F26">
         <v>740</v>
@@ -961,7 +961,7 @@
         <v>250</v>
       </c>
       <c r="E27">
-        <v>125</v>
+        <v>50</v>
       </c>
       <c r="F27">
         <v>770</v>
@@ -981,7 +981,7 @@
         <v>260</v>
       </c>
       <c r="E28">
-        <v>130</v>
+        <v>52</v>
       </c>
       <c r="F28">
         <v>800</v>
@@ -1001,7 +1001,7 @@
         <v>270</v>
       </c>
       <c r="E29">
-        <v>135</v>
+        <v>54</v>
       </c>
       <c r="F29">
         <v>830</v>
@@ -1021,7 +1021,7 @@
         <v>280</v>
       </c>
       <c r="E30">
-        <v>140</v>
+        <v>56</v>
       </c>
       <c r="F30">
         <v>860</v>
@@ -1041,7 +1041,7 @@
         <v>290</v>
       </c>
       <c r="E31">
-        <v>145</v>
+        <v>58</v>
       </c>
       <c r="F31">
         <v>890</v>
@@ -1061,7 +1061,7 @@
         <v>300</v>
       </c>
       <c r="E32">
-        <v>150</v>
+        <v>60</v>
       </c>
       <c r="F32">
         <v>920</v>
@@ -1081,7 +1081,7 @@
         <v>310</v>
       </c>
       <c r="E33">
-        <v>155</v>
+        <v>62</v>
       </c>
       <c r="F33">
         <v>950</v>
@@ -1101,7 +1101,7 @@
         <v>320</v>
       </c>
       <c r="E34">
-        <v>160</v>
+        <v>64</v>
       </c>
       <c r="F34">
         <v>980</v>
@@ -1121,7 +1121,7 @@
         <v>330</v>
       </c>
       <c r="E35">
-        <v>165</v>
+        <v>66</v>
       </c>
       <c r="F35">
         <v>1010</v>
@@ -1141,7 +1141,7 @@
         <v>340</v>
       </c>
       <c r="E36">
-        <v>170</v>
+        <v>68</v>
       </c>
       <c r="F36">
         <v>1040</v>
@@ -1161,7 +1161,7 @@
         <v>350</v>
       </c>
       <c r="E37">
-        <v>175</v>
+        <v>70</v>
       </c>
       <c r="F37">
         <v>1070</v>
@@ -1181,7 +1181,7 @@
         <v>360</v>
       </c>
       <c r="E38">
-        <v>180</v>
+        <v>72</v>
       </c>
       <c r="F38">
         <v>1100</v>
@@ -1201,7 +1201,7 @@
         <v>370</v>
       </c>
       <c r="E39">
-        <v>185</v>
+        <v>74</v>
       </c>
       <c r="F39">
         <v>1130</v>
@@ -1221,7 +1221,7 @@
         <v>380</v>
       </c>
       <c r="E40">
-        <v>190</v>
+        <v>76</v>
       </c>
       <c r="F40">
         <v>1160</v>
@@ -1241,7 +1241,7 @@
         <v>390</v>
       </c>
       <c r="E41">
-        <v>195</v>
+        <v>78</v>
       </c>
       <c r="F41">
         <v>1190</v>
@@ -1261,7 +1261,7 @@
         <v>400</v>
       </c>
       <c r="E42">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="F42">
         <v>1220</v>
@@ -1281,7 +1281,7 @@
         <v>410</v>
       </c>
       <c r="E43">
-        <v>205</v>
+        <v>82</v>
       </c>
       <c r="F43">
         <v>1250</v>
@@ -1301,7 +1301,7 @@
         <v>420</v>
       </c>
       <c r="E44">
-        <v>210</v>
+        <v>84</v>
       </c>
       <c r="F44">
         <v>1280</v>
@@ -1321,7 +1321,7 @@
         <v>430</v>
       </c>
       <c r="E45">
-        <v>215</v>
+        <v>86</v>
       </c>
       <c r="F45">
         <v>1310</v>
@@ -1341,7 +1341,7 @@
         <v>440</v>
       </c>
       <c r="E46">
-        <v>220</v>
+        <v>88</v>
       </c>
       <c r="F46">
         <v>1340</v>
@@ -1361,7 +1361,7 @@
         <v>450</v>
       </c>
       <c r="E47">
-        <v>225</v>
+        <v>90</v>
       </c>
       <c r="F47">
         <v>1370</v>
@@ -1381,7 +1381,7 @@
         <v>460</v>
       </c>
       <c r="E48">
-        <v>230</v>
+        <v>92</v>
       </c>
       <c r="F48">
         <v>1400</v>
@@ -1401,7 +1401,7 @@
         <v>470</v>
       </c>
       <c r="E49">
-        <v>235</v>
+        <v>94</v>
       </c>
       <c r="F49">
         <v>1430</v>
@@ -1421,7 +1421,7 @@
         <v>480</v>
       </c>
       <c r="E50">
-        <v>240</v>
+        <v>96</v>
       </c>
       <c r="F50">
         <v>1460</v>
@@ -1441,7 +1441,7 @@
         <v>490</v>
       </c>
       <c r="E51">
-        <v>245</v>
+        <v>98</v>
       </c>
       <c r="F51">
         <v>1490</v>
@@ -1461,7 +1461,7 @@
         <v>500</v>
       </c>
       <c r="E52">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="F52">
         <v>0</v>
@@ -1470,5 +1470,6 @@
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Server/Common/GameDatasheet/Original_Warrior_Level_Data.xlsx
+++ b/Server/Common/GameDatasheet/Original_Warrior_Level_Data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\zmwps\Desktop\Project_MMORPG\Server\Common\GameDatasheet\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A04FBD9F-480C-4F8C-8C6A-8DCE2E80EA35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77B5F409-868C-49AA-BABB-979052EDF32C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{FDA0E9BE-2965-48E7-917D-7535984AEDF4}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="11">
   <si>
     <t>level</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -52,6 +52,22 @@
   </si>
   <si>
     <t>exp_requirement</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>max_hp_increment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>max_mp_increment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pa_increment</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ma_increment</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -416,7 +432,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{88E1A4D9-35B0-4CC7-8009-2E8D5C187D72}">
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:J52"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="7.296875" bestFit="1" customWidth="1"/>
@@ -425,9 +441,13 @@
     <col min="4" max="4" width="12.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.296875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16.3984375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.09765625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.69921875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -446,8 +466,20 @@
       <c r="F1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -466,8 +498,20 @@
       <c r="F2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G2" t="s">
+        <v>3</v>
+      </c>
+      <c r="H2" t="s">
+        <v>3</v>
+      </c>
+      <c r="I2" t="s">
+        <v>3</v>
+      </c>
+      <c r="J2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A3">
         <v>1</v>
       </c>
@@ -486,8 +530,20 @@
       <c r="F3">
         <v>50</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G3">
+        <v>500</v>
+      </c>
+      <c r="H3">
+        <v>100</v>
+      </c>
+      <c r="I3">
+        <v>10</v>
+      </c>
+      <c r="J3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A4">
         <v>2</v>
       </c>
@@ -506,8 +562,24 @@
       <c r="F4">
         <v>80</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G4">
+        <f>B4-B3</f>
+        <v>100</v>
+      </c>
+      <c r="H4">
+        <f>C4-C3</f>
+        <v>100</v>
+      </c>
+      <c r="I4">
+        <f>D4-D3</f>
+        <v>10</v>
+      </c>
+      <c r="J4">
+        <f>E4-E3</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A5">
         <v>3</v>
       </c>
@@ -526,8 +598,24 @@
       <c r="F5">
         <v>110</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G5">
+        <f t="shared" ref="G5:G52" si="0">B5-B4</f>
+        <v>100</v>
+      </c>
+      <c r="H5">
+        <f t="shared" ref="H5:H52" si="1">C5-C4</f>
+        <v>100</v>
+      </c>
+      <c r="I5">
+        <f t="shared" ref="I5:I52" si="2">D5-D4</f>
+        <v>10</v>
+      </c>
+      <c r="J5">
+        <f t="shared" ref="J5:J52" si="3">E5-E4</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A6">
         <v>4</v>
       </c>
@@ -546,8 +634,24 @@
       <c r="F6">
         <v>140</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G6">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="I6">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A7">
         <v>5</v>
       </c>
@@ -566,8 +670,24 @@
       <c r="F7">
         <v>170</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G7">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="I7">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A8">
         <v>6</v>
       </c>
@@ -586,8 +706,24 @@
       <c r="F8">
         <v>200</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G8">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="I8">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A9">
         <v>7</v>
       </c>
@@ -606,8 +742,24 @@
       <c r="F9">
         <v>230</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G9">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="I9">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A10">
         <v>8</v>
       </c>
@@ -626,8 +778,24 @@
       <c r="F10">
         <v>260</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G10">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="I10">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A11">
         <v>9</v>
       </c>
@@ -646,8 +814,24 @@
       <c r="F11">
         <v>290</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G11">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="I11">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A12">
         <v>10</v>
       </c>
@@ -666,8 +850,24 @@
       <c r="F12">
         <v>320</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G12">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="I12">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A13">
         <v>11</v>
       </c>
@@ -686,8 +886,24 @@
       <c r="F13">
         <v>350</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G13">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="I13">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A14">
         <v>12</v>
       </c>
@@ -706,8 +922,24 @@
       <c r="F14">
         <v>380</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G14">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H14">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="I14">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A15">
         <v>13</v>
       </c>
@@ -726,8 +958,24 @@
       <c r="F15">
         <v>410</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G15">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="I15">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A16">
         <v>14</v>
       </c>
@@ -746,8 +994,24 @@
       <c r="F16">
         <v>440</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G16">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="I16">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="J16">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A17">
         <v>15</v>
       </c>
@@ -766,8 +1030,24 @@
       <c r="F17">
         <v>470</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G17">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="I17">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A18">
         <v>16</v>
       </c>
@@ -786,8 +1066,24 @@
       <c r="F18">
         <v>500</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G18">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H18">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="I18">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="J18">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A19">
         <v>17</v>
       </c>
@@ -806,8 +1102,24 @@
       <c r="F19">
         <v>530</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G19">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H19">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="I19">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="J19">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A20">
         <v>18</v>
       </c>
@@ -826,8 +1138,24 @@
       <c r="F20">
         <v>560</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G20">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H20">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="I20">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="J20">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A21">
         <v>19</v>
       </c>
@@ -846,8 +1174,24 @@
       <c r="F21">
         <v>590</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G21">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H21">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="I21">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="J21">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A22">
         <v>20</v>
       </c>
@@ -866,8 +1210,24 @@
       <c r="F22">
         <v>620</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G22">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H22">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="I22">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="J22">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A23">
         <v>21</v>
       </c>
@@ -886,8 +1246,24 @@
       <c r="F23">
         <v>650</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G23">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H23">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="I23">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="J23">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A24">
         <v>22</v>
       </c>
@@ -906,8 +1282,24 @@
       <c r="F24">
         <v>680</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G24">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H24">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="I24">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="J24">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A25">
         <v>23</v>
       </c>
@@ -926,8 +1318,24 @@
       <c r="F25">
         <v>710</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G25">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H25">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="I25">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="J25">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A26">
         <v>24</v>
       </c>
@@ -946,8 +1354,24 @@
       <c r="F26">
         <v>740</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G26">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H26">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="I26">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="J26">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A27">
         <v>25</v>
       </c>
@@ -966,8 +1390,24 @@
       <c r="F27">
         <v>770</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G27">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H27">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="I27">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="J27">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A28">
         <v>26</v>
       </c>
@@ -986,8 +1426,24 @@
       <c r="F28">
         <v>800</v>
       </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G28">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H28">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="I28">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="J28">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A29">
         <v>27</v>
       </c>
@@ -1006,8 +1462,24 @@
       <c r="F29">
         <v>830</v>
       </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G29">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H29">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="I29">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="J29">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A30">
         <v>28</v>
       </c>
@@ -1026,8 +1498,24 @@
       <c r="F30">
         <v>860</v>
       </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G30">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H30">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="I30">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="J30">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A31">
         <v>29</v>
       </c>
@@ -1046,8 +1534,24 @@
       <c r="F31">
         <v>890</v>
       </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G31">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H31">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="I31">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="J31">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A32">
         <v>30</v>
       </c>
@@ -1066,8 +1570,24 @@
       <c r="F32">
         <v>920</v>
       </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G32">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H32">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="I32">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="J32">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A33">
         <v>31</v>
       </c>
@@ -1086,8 +1606,24 @@
       <c r="F33">
         <v>950</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G33">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H33">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="I33">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="J33">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A34">
         <v>32</v>
       </c>
@@ -1106,8 +1642,24 @@
       <c r="F34">
         <v>980</v>
       </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G34">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H34">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="I34">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="J34">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A35">
         <v>33</v>
       </c>
@@ -1126,8 +1678,24 @@
       <c r="F35">
         <v>1010</v>
       </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G35">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H35">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="I35">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="J35">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A36">
         <v>34</v>
       </c>
@@ -1146,8 +1714,24 @@
       <c r="F36">
         <v>1040</v>
       </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G36">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H36">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="I36">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="J36">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A37">
         <v>35</v>
       </c>
@@ -1166,8 +1750,24 @@
       <c r="F37">
         <v>1070</v>
       </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G37">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H37">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="I37">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="J37">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A38">
         <v>36</v>
       </c>
@@ -1186,8 +1786,24 @@
       <c r="F38">
         <v>1100</v>
       </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G38">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H38">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="I38">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="J38">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A39">
         <v>37</v>
       </c>
@@ -1206,8 +1822,24 @@
       <c r="F39">
         <v>1130</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G39">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H39">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="I39">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="J39">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A40">
         <v>38</v>
       </c>
@@ -1226,8 +1858,24 @@
       <c r="F40">
         <v>1160</v>
       </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G40">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H40">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="I40">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="J40">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A41">
         <v>39</v>
       </c>
@@ -1246,8 +1894,24 @@
       <c r="F41">
         <v>1190</v>
       </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G41">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H41">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="I41">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="J41">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A42">
         <v>40</v>
       </c>
@@ -1266,8 +1930,24 @@
       <c r="F42">
         <v>1220</v>
       </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G42">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H42">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="I42">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="J42">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A43">
         <v>41</v>
       </c>
@@ -1286,8 +1966,24 @@
       <c r="F43">
         <v>1250</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G43">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H43">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="I43">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="J43">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A44">
         <v>42</v>
       </c>
@@ -1306,8 +2002,24 @@
       <c r="F44">
         <v>1280</v>
       </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G44">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H44">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="I44">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="J44">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A45">
         <v>43</v>
       </c>
@@ -1326,8 +2038,24 @@
       <c r="F45">
         <v>1310</v>
       </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G45">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H45">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="I45">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="J45">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A46">
         <v>44</v>
       </c>
@@ -1346,8 +2074,24 @@
       <c r="F46">
         <v>1340</v>
       </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G46">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H46">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="I46">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="J46">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A47">
         <v>45</v>
       </c>
@@ -1366,8 +2110,24 @@
       <c r="F47">
         <v>1370</v>
       </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G47">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H47">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="I47">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="J47">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A48">
         <v>46</v>
       </c>
@@ -1386,8 +2146,24 @@
       <c r="F48">
         <v>1400</v>
       </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G48">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H48">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="I48">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="J48">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A49">
         <v>47</v>
       </c>
@@ -1406,8 +2182,24 @@
       <c r="F49">
         <v>1430</v>
       </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G49">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H49">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="I49">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="J49">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A50">
         <v>48</v>
       </c>
@@ -1426,8 +2218,24 @@
       <c r="F50">
         <v>1460</v>
       </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G50">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H50">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="I50">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="J50">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A51">
         <v>49</v>
       </c>
@@ -1446,8 +2254,24 @@
       <c r="F51">
         <v>1490</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G51">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H51">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="I51">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="J51">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A52">
         <v>50</v>
       </c>
@@ -1465,6 +2289,22 @@
       </c>
       <c r="F52">
         <v>0</v>
+      </c>
+      <c r="G52">
+        <f t="shared" si="0"/>
+        <v>100</v>
+      </c>
+      <c r="H52">
+        <f t="shared" si="1"/>
+        <v>100</v>
+      </c>
+      <c r="I52">
+        <f t="shared" si="2"/>
+        <v>10</v>
+      </c>
+      <c r="J52">
+        <f t="shared" si="3"/>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
